--- a/SELLER-READY-BOARD-OPERATIONS.xlsx
+++ b/SELLER-READY-BOARD-OPERATIONS.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="R117655bdca9b4ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="셀러 레디 보드" sheetId="2" r:id="Rb793f0d5304440c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상황 대응" sheetId="3" r:id="R1ac7d786887d4423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협업·인계" sheetId="4" r:id="Ra869dca1a2b14bc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VOC 개선" sheetId="5" r:id="R022d27885cc94c7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI·출처" sheetId="6" r:id="Rd5981be16ca34fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="R64bf1c6f941546a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="셀러 레디 보드" sheetId="2" r:id="Re7e7ecfcc41045b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상황 대응" sheetId="3" r:id="R175474ce5744426f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협업·인계" sheetId="4" r:id="R967a641c3d374045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VOC 개선" sheetId="5" r:id="R0d6c87c29c4747ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI·출처" sheetId="6" r:id="Rdad1b126b7a4435e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -189,7 +189,7 @@
         <x:color rgb="FF8A2F25"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE8E6"/>
         </x:patternFill>
       </x:fill>
@@ -200,7 +200,7 @@
         <x:color rgb="FF8B5A11"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1D6"/>
         </x:patternFill>
       </x:fill>
@@ -211,7 +211,7 @@
         <x:color rgb="FF24568A"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE5F0FF"/>
         </x:patternFill>
       </x:fill>
@@ -222,7 +222,7 @@
         <x:color rgb="FF5F3B8D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF1EAFE"/>
         </x:patternFill>
       </x:fill>
@@ -507,7 +507,7 @@
         <x:v>써보는 방법</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>1주간 현재 상태를 기록하고 다음 1주간 보드를 사용해 변화와 기록 시간을 확인</x:v>
+        <x:v>1~2일 기준 맞춤 → 3~7일 매일 사용 → 8~12일 반복 문의 안내문 개선 → 13~14일 유지·수정·중단 결정</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12"/>
@@ -883,7 +883,7 @@
         <x:v>판매 준비</x:v>
       </x:c>
       <x:c r="D7" s="26" t="str">
-        <x:v>대표 이미지와 상품 상세 설명이 비어 있음</x:v>
+        <x:v>실제 재고와 등록 재고가 다르고 주문 접수 알림 확인이 안 됨</x:v>
       </x:c>
       <x:c r="E7" s="26" t="n">
         <x:v>2</x:v>
@@ -901,7 +901,7 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="J7" s="26" t="str">
-        <x:v>필수 상품 정보 체크리스트 전송 후 완료 항목을 함께 확인</x:v>
+        <x:v>재고 일치와 주문 접수 준비를 확인하고 필요하면 수량 수정·판매 중지 경로 안내</x:v>
       </x:c>
       <x:c r="K7" s="28" t="str">
         <x:f>IF(I7="Y","정확성 확인",IF(OR(E7&gt;=5,F7&gt;=2),"장기 대기·재문의",IF(AND(G7&gt;=0,G7&lt;=3),"판매 준비 임박",IF(OR(H7="",H7="미배정",J7=""),"담당자 미배정","일반 진행"))))</x:f>
@@ -911,10 +911,10 @@
         <x:v>오늘 16:00</x:v>
       </x:c>
       <x:c r="M7" s="12" t="str">
-        <x:v>필수 상품 정보 등록 및 노출 확인</x:v>
+        <x:v>재고 일치, 품절 상품 숨김, 테스트 주문 알림 확인</x:v>
       </x:c>
       <x:c r="N7" s="12" t="str">
-        <x:v>정보 부족 상태의 판매 시작과 고객 이탈</x:v>
+        <x:v>오픈 후 주문 취소와 셀러 매출 손실</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
@@ -1475,28 +1475,28 @@
     </x:row>
     <x:row r="7" ht="88" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>오픈 하루 전 상품 정보가 미완료된 셀러</x:v>
+        <x:v>오픈 하루 전 재고와 주문 접수 준비가 불확실한 셀러</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>대표 이미지와 상세 설명이 비어 있지만 오픈 예정일이 하루 남음</x:v>
+        <x:v>실제 재고와 등록 재고가 다르고 주문 접수 알림 확인이 안 된 채 오픈이 하루 남음</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>필수 정보, 이미지 규격, 상품명·카테고리·판매 조건, 남은 처리 여력</x:v>
+        <x:v>실재고·등록 수량, 품절 상품 노출, 주문 접수 기기·알림, 테스트 주문 결과</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
-        <x:v>하루 처리 여력 일부를 배정하되 정확성 검토를 생략하지 않음</x:v>
+        <x:v>오픈 일정만 맞추지 않고 주문 취소 가능성을 먼저 줄임</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>상품 운영과 마케팅 지원이 필수 항목과 프로모션 문구를 교차 확인</x:v>
+        <x:v>상품 운영과 주문 지원이 재고 수정·판매 중지 경로와 알림 상태를 함께 확인</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>오늘 완료할 항목과 확인 시간을 셀러에게 명확히 전달</x:v>
+        <x:v>수량 수정 또는 판매 중지 방법과 테스트 주문 확인 시간을 셀러에게 안내</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
-        <x:v>필수 정보 등록, 앱 노출과 판매 조건 확인</x:v>
+        <x:v>재고 일치, 품절 상품 숨김, 테스트 주문 알림 확인</x:v>
       </x:c>
       <x:c r="H7" s="12" t="str">
-        <x:v>오픈 D-3 자동 점검 항목에 이미지·상세 설명 추가</x:v>
+        <x:v>오픈 전 점검표에 재고 일치와 주문 접수 알림 확인 추가</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1909,19 +1909,19 @@
     </x:row>
     <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>90백분위 대기</x:v>
+        <x:v>대기시간 상위 10% 기준</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>업무 90%가 포함되는 대기일</x:v>
+        <x:v>업무 10건 중 9건이 이 시간 안에 포함되는 대기일</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>대기일 90백분위</x:v>
+        <x:v>대기일 상위 10% 경계값</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
         <x:v>최장 미처리</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>꼬리 대기 감소</x:v>
+        <x:v>긴 대기 꼬리 감소</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
         <x:v>완료·미완료 분리</x:v>
@@ -2013,13 +2013,13 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12" t="str">
-        <x:v>상품 등록</x:v>
+        <x:v>서비스 소개</x:v>
       </x:c>
       <x:c r="B14" s="12" t="str">
-        <x:v>배민스토어 상품 등록·수정 관리</x:v>
+        <x:v>배민스토어의 이해</x:v>
       </x:c>
       <x:c r="C14" s="12" t="str">
-        <x:v>https://ceo.baemin.com/guide/11802</x:v>
+        <x:v>https://ceo.baemin.com/guide/10554</x:v>
       </x:c>
       <x:c r="D14" s="12" t="str"/>
       <x:c r="E14" s="12" t="str"/>
@@ -2027,13 +2027,13 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12" t="str">
-        <x:v>상품 상세</x:v>
+        <x:v>주문·재고</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>배민스토어 상품 상세 설명 변경하기</x:v>
+        <x:v>주문 취소와 재고 관리 노하우</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str">
-        <x:v>https://ceo.baemin.com/guide/12796</x:v>
+        <x:v>https://ceo.baemin.com/guide/12824</x:v>
       </x:c>
       <x:c r="D15" s="12" t="str"/>
       <x:c r="E15" s="12" t="str"/>
@@ -2041,13 +2041,13 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="12" t="str">
-        <x:v>정산</x:v>
+        <x:v>상품 등록</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>배민스토어 묶음형 정산 방식</x:v>
+        <x:v>배민스토어 상품 등록·수정 관리</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
-        <x:v>https://ceo.baemin.com/guide/12206</x:v>
+        <x:v>https://ceo.baemin.com/guide/11802</x:v>
       </x:c>
       <x:c r="D16" s="12" t="str"/>
       <x:c r="E16" s="12" t="str"/>
@@ -2055,17 +2055,31 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="12" t="str">
-        <x:v>마케팅 참고</x:v>
+        <x:v>상품 상세</x:v>
       </x:c>
       <x:c r="B17" s="12" t="str">
-        <x:v>배민배달을 시작하는 파트너님을 위한 마케팅 꿀팁</x:v>
+        <x:v>배민스토어 상품 상세 설명 변경하기</x:v>
       </x:c>
       <x:c r="C17" s="12" t="str">
-        <x:v>https://ceo.baemin.com/guide/12232</x:v>
+        <x:v>https://ceo.baemin.com/guide/12796</x:v>
       </x:c>
       <x:c r="D17" s="12" t="str"/>
       <x:c r="E17" s="12" t="str"/>
       <x:c r="F17" s="12" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>정산</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>배민스토어 묶음형 정산 방식</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>https://ceo.baemin.com/guide/12206</x:v>
+      </x:c>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/SELLER-READY-BOARD-OPERATIONS.xlsx
+++ b/SELLER-READY-BOARD-OPERATIONS.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="R64bf1c6f941546a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="셀러 레디 보드" sheetId="2" r:id="Re7e7ecfcc41045b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상황 대응" sheetId="3" r:id="R175474ce5744426f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협업·인계" sheetId="4" r:id="R967a641c3d374045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VOC 개선" sheetId="5" r:id="R0d6c87c29c4747ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI·출처" sheetId="6" r:id="Rdad1b126b7a4435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" r:id="R3a993cb495424715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="셀러 레디 보드" sheetId="2" r:id="Rd30172fe18014e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상황 대응" sheetId="3" r:id="Rc4efe0f08ec847e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="협업 및 인계" sheetId="4" r:id="R6affb12aac4b4b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VOC 개선" sheetId="5" r:id="Ra976c053fb714377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI 및 출처" sheetId="6" r:id="Rca4ff335884048d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -479,7 +479,7 @@
         <x:v>제가 만든 방법</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
-        <x:v>정보 오류·오래 기다린 건·오픈 임박·담당자 미배정을 나눠 다음 행동까지 기록</x:v>
+        <x:v>정보 오류, 오래 기다린 건, 오픈 임박, 담당자 미배정을 나눠 다음 행동까지 기록</x:v>
       </x:c>
       <x:c r="C5" s="12"/>
       <x:c r="D5" s="12"/>
@@ -493,7 +493,7 @@
         <x:v>기대하는 변화</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>재문의와 재작업을 줄이고, 잘못된 상품·정산 정보가 고객에게 보이는 상황 예방</x:v>
+        <x:v>재문의와 재작업을 줄이고, 잘못된 상품과 정산 정보가 고객에게 보이는 상황 예방</x:v>
       </x:c>
       <x:c r="C6" s="12"/>
       <x:c r="D6" s="12"/>
@@ -507,7 +507,7 @@
         <x:v>써보는 방법</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>1~2일 기준 맞춤 → 3~7일 매일 사용 → 8~12일 반복 문의 안내문 개선 → 13~14일 유지·수정·중단 결정</x:v>
+        <x:v>1~2일 기준 맞춤 → 3~7일 매일 사용 → 8~12일 반복 문의 안내문 개선 → 13~14일 유지, 수정 또는 중단 결정</x:v>
       </x:c>
       <x:c r="C7" s="12"/>
       <x:c r="D7" s="12"/>
@@ -550,7 +550,7 @@
         <x:v>정확성 확인</x:v>
       </x:c>
       <x:c r="C11" s="19" t="str">
-        <x:v>장기 대기·재문의</x:v>
+        <x:v>장기 대기 및 재문의</x:v>
       </x:c>
       <x:c r="D11" s="19" t="str">
         <x:v>판매 준비 임박</x:v>
@@ -611,7 +611,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
-        <x:v>셀러 레디 보드에서 대기일·재문의·오픈일·담당자·오류 여부를 갱신합니다.</x:v>
+        <x:v>대기일, 재문의, 오픈일, 담당자, 오류 여부</x:v>
       </x:c>
       <x:c r="C15" s="12" t="str"/>
       <x:c r="D15" s="12" t="str"/>
@@ -814,7 +814,7 @@
         <x:v>카테고리와 중개이용료 기준 확인 후 수정 경로 안내</x:v>
       </x:c>
       <x:c r="K5" s="28" t="str">
-        <x:f>IF(I5="Y","정확성 확인",IF(OR(E5&gt;=5,F5&gt;=2),"장기 대기·재문의",IF(AND(G5&gt;=0,G5&lt;=3),"판매 준비 임박",IF(OR(H5="",H5="미배정",J5=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I5="Y","정확성 확인",IF(OR(E5&gt;=5,F5&gt;=2),"장기 대기 및 재문의",IF(AND(G5&gt;=0,G5&lt;=3),"판매 준비 임박",IF(OR(H5="",H5="미배정",J5=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>정확성 확인</x:v>
       </x:c>
       <x:c r="L5" s="12" t="str">
@@ -859,8 +859,8 @@
         <x:v>불일치 항목 한 번에 정리해 보완 위치와 재확인 시점 안내</x:v>
       </x:c>
       <x:c r="K6" s="28" t="str">
-        <x:f>IF(I6="Y","정확성 확인",IF(OR(E6&gt;=5,F6&gt;=2),"장기 대기·재문의",IF(AND(G6&gt;=0,G6&lt;=3),"판매 준비 임박",IF(OR(H6="",H6="미배정",J6=""),"담당자 미배정","일반 진행"))))</x:f>
-        <x:v>장기 대기·재문의</x:v>
+        <x:f>IF(I6="Y","정확성 확인",IF(OR(E6&gt;=5,F6&gt;=2),"장기 대기 및 재문의",IF(AND(G6&gt;=0,G6&lt;=3),"판매 준비 임박",IF(OR(H6="",H6="미배정",J6=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:v>장기 대기 및 재문의</x:v>
       </x:c>
       <x:c r="L6" s="12" t="str">
         <x:v>오늘 11:00</x:v>
@@ -901,10 +901,10 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="J7" s="26" t="str">
-        <x:v>재고 일치와 주문 접수 준비를 확인하고 필요하면 수량 수정·판매 중지 경로 안내</x:v>
+        <x:v>재고 일치와 주문 접수 준비를 확인하고 필요하면 수량 수정 또는 판매 중지 경로 안내</x:v>
       </x:c>
       <x:c r="K7" s="28" t="str">
-        <x:f>IF(I7="Y","정확성 확인",IF(OR(E7&gt;=5,F7&gt;=2),"장기 대기·재문의",IF(AND(G7&gt;=0,G7&lt;=3),"판매 준비 임박",IF(OR(H7="",H7="미배정",J7=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I7="Y","정확성 확인",IF(OR(E7&gt;=5,F7&gt;=2),"장기 대기 및 재문의",IF(AND(G7&gt;=0,G7&lt;=3),"판매 준비 임박",IF(OR(H7="",H7="미배정",J7=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>판매 준비 임박</x:v>
       </x:c>
       <x:c r="L7" s="12" t="str">
@@ -949,14 +949,14 @@
         <x:v>정산 담당자 배정 후 확인 필요 항목과 회신 시점 기록</x:v>
       </x:c>
       <x:c r="K8" s="28" t="str">
-        <x:f>IF(I8="Y","정확성 확인",IF(OR(E8&gt;=5,F8&gt;=2),"장기 대기·재문의",IF(AND(G8&gt;=0,G8&lt;=3),"판매 준비 임박",IF(OR(H8="",H8="미배정",J8=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I8="Y","정확성 확인",IF(OR(E8&gt;=5,F8&gt;=2),"장기 대기 및 재문의",IF(AND(G8&gt;=0,G8&lt;=3),"판매 준비 임박",IF(OR(H8="",H8="미배정",J8=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>담당자 미배정</x:v>
       </x:c>
       <x:c r="L8" s="12" t="str">
         <x:v>오늘 12:00</x:v>
       </x:c>
       <x:c r="M8" s="12" t="str">
-        <x:v>담당자·확인 결과·셀러 안내 기록</x:v>
+        <x:v>담당자, 확인 결과, 셀러 안내 기록</x:v>
       </x:c>
       <x:c r="N8" s="12" t="str">
         <x:v>오픈 이후 정산 문의와 책임 공백</x:v>
@@ -994,7 +994,7 @@
         <x:v>예정 일정에 따라 계약 서명 여부 확인</x:v>
       </x:c>
       <x:c r="K9" s="28" t="str">
-        <x:f>IF(I9="Y","정확성 확인",IF(OR(E9&gt;=5,F9&gt;=2),"장기 대기·재문의",IF(AND(G9&gt;=0,G9&lt;=3),"판매 준비 임박",IF(OR(H9="",H9="미배정",J9=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I9="Y","정확성 확인",IF(OR(E9&gt;=5,F9&gt;=2),"장기 대기 및 재문의",IF(AND(G9&gt;=0,G9&lt;=3),"판매 준비 임박",IF(OR(H9="",H9="미배정",J9=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>일반 진행</x:v>
       </x:c>
       <x:c r="L9" s="12" t="str">
@@ -1039,8 +1039,8 @@
         <x:v>상품 등록에서 기존 옵션을 연결하도록 화면 경로 안내</x:v>
       </x:c>
       <x:c r="K10" s="28" t="str">
-        <x:f>IF(I10="Y","정확성 확인",IF(OR(E10&gt;=5,F10&gt;=2),"장기 대기·재문의",IF(AND(G10&gt;=0,G10&lt;=3),"판매 준비 임박",IF(OR(H10="",H10="미배정",J10=""),"담당자 미배정","일반 진행"))))</x:f>
-        <x:v>장기 대기·재문의</x:v>
+        <x:f>IF(I10="Y","정확성 확인",IF(OR(E10&gt;=5,F10&gt;=2),"장기 대기 및 재문의",IF(AND(G10&gt;=0,G10&lt;=3),"판매 준비 임박",IF(OR(H10="",H10="미배정",J10=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:v>장기 대기 및 재문의</x:v>
       </x:c>
       <x:c r="L10" s="12" t="str">
         <x:v>오늘 15:00</x:v>
@@ -1081,10 +1081,10 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="J11" s="26" t="str">
-        <x:v>판매 기간·가격·노출 문구를 마케팅 담당과 교차 확인</x:v>
+        <x:v>판매 기간, 가격, 노출 문구</x:v>
       </x:c>
       <x:c r="K11" s="28" t="str">
-        <x:f>IF(I11="Y","정확성 확인",IF(OR(E11&gt;=5,F11&gt;=2),"장기 대기·재문의",IF(AND(G11&gt;=0,G11&lt;=3),"판매 준비 임박",IF(OR(H11="",H11="미배정",J11=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I11="Y","정확성 확인",IF(OR(E11&gt;=5,F11&gt;=2),"장기 대기 및 재문의",IF(AND(G11&gt;=0,G11&lt;=3),"판매 준비 임박",IF(OR(H11="",H11="미배정",J11=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>판매 준비 임박</x:v>
       </x:c>
       <x:c r="L11" s="12" t="str">
@@ -1108,7 +1108,7 @@
         <x:v>상품 등록</x:v>
       </x:c>
       <x:c r="D12" s="26" t="str">
-        <x:v>상품명에 수량·중량 정보가 빠짐</x:v>
+        <x:v>수량과 중량</x:v>
       </x:c>
       <x:c r="E12" s="26" t="n">
         <x:v>2</x:v>
@@ -1129,7 +1129,7 @@
         <x:v>상품명과 상세 정보의 필수 표현 확인 후 수정 요청</x:v>
       </x:c>
       <x:c r="K12" s="28" t="str">
-        <x:f>IF(I12="Y","정확성 확인",IF(OR(E12&gt;=5,F12&gt;=2),"장기 대기·재문의",IF(AND(G12&gt;=0,G12&lt;=3),"판매 준비 임박",IF(OR(H12="",H12="미배정",J12=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I12="Y","정확성 확인",IF(OR(E12&gt;=5,F12&gt;=2),"장기 대기 및 재문의",IF(AND(G12&gt;=0,G12&lt;=3),"판매 준비 임박",IF(OR(H12="",H12="미배정",J12=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>정확성 확인</x:v>
       </x:c>
       <x:c r="L12" s="12" t="str">
@@ -1174,7 +1174,7 @@
         <x:v>셀프서비스 내 정산내역과 명세서 다운로드 경로 안내</x:v>
       </x:c>
       <x:c r="K13" s="28" t="str">
-        <x:f>IF(I13="Y","정확성 확인",IF(OR(E13&gt;=5,F13&gt;=2),"장기 대기·재문의",IF(AND(G13&gt;=0,G13&lt;=3),"판매 준비 임박",IF(OR(H13="",H13="미배정",J13=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I13="Y","정확성 확인",IF(OR(E13&gt;=5,F13&gt;=2),"장기 대기 및 재문의",IF(AND(G13&gt;=0,G13&lt;=3),"판매 준비 임박",IF(OR(H13="",H13="미배정",J13=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>일반 진행</x:v>
       </x:c>
       <x:c r="L13" s="12" t="str">
@@ -1219,7 +1219,7 @@
         <x:v>계약 지원 담당자를 배정하고 필요 서류를 한 번에 확정</x:v>
       </x:c>
       <x:c r="K14" s="28" t="str">
-        <x:f>IF(I14="Y","정확성 확인",IF(OR(E14&gt;=5,F14&gt;=2),"장기 대기·재문의",IF(AND(G14&gt;=0,G14&lt;=3),"판매 준비 임박",IF(OR(H14="",H14="미배정",J14=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I14="Y","정확성 확인",IF(OR(E14&gt;=5,F14&gt;=2),"장기 대기 및 재문의",IF(AND(G14&gt;=0,G14&lt;=3),"판매 준비 임박",IF(OR(H14="",H14="미배정",J14=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>담당자 미배정</x:v>
       </x:c>
       <x:c r="L14" s="12" t="str">
@@ -1264,7 +1264,7 @@
         <x:v>운영시간과 주문 가능 노출 조건 확인</x:v>
       </x:c>
       <x:c r="K15" s="28" t="str">
-        <x:f>IF(I15="Y","정확성 확인",IF(OR(E15&gt;=5,F15&gt;=2),"장기 대기·재문의",IF(AND(G15&gt;=0,G15&lt;=3),"판매 준비 임박",IF(OR(H15="",H15="미배정",J15=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:f>IF(I15="Y","정확성 확인",IF(OR(E15&gt;=5,F15&gt;=2),"장기 대기 및 재문의",IF(AND(G15&gt;=0,G15&lt;=3),"판매 준비 임박",IF(OR(H15="",H15="미배정",J15=""),"담당자 미배정","일반 진행"))))</x:f>
         <x:v>일반 진행</x:v>
       </x:c>
       <x:c r="L15" s="12" t="str">
@@ -1306,11 +1306,11 @@
         <x:v>N</x:v>
       </x:c>
       <x:c r="J16" s="26" t="str">
-        <x:v>가능한 파일 형식·크기와 업로드 위치를 한 번에 안내</x:v>
+        <x:v>파일 형식과 크기</x:v>
       </x:c>
       <x:c r="K16" s="28" t="str">
-        <x:f>IF(I16="Y","정확성 확인",IF(OR(E16&gt;=5,F16&gt;=2),"장기 대기·재문의",IF(AND(G16&gt;=0,G16&lt;=3),"판매 준비 임박",IF(OR(H16="",H16="미배정",J16=""),"담당자 미배정","일반 진행"))))</x:f>
-        <x:v>장기 대기·재문의</x:v>
+        <x:f>IF(I16="Y","정확성 확인",IF(OR(E16&gt;=5,F16&gt;=2),"장기 대기 및 재문의",IF(AND(G16&gt;=0,G16&lt;=3),"판매 준비 임박",IF(OR(H16="",H16="미배정",J16=""),"담당자 미배정","일반 진행"))))</x:f>
+        <x:v>장기 대기 및 재문의</x:v>
       </x:c>
       <x:c r="L16" s="12" t="str">
         <x:v>오늘 13:30</x:v>
@@ -1332,7 +1332,7 @@
       <x:formula>$K5="정확성 확인"</x:formula>
     </x:cfRule>
     <x:cfRule type="expression" dxfId="1" priority="2">
-      <x:formula>$K5="장기 대기·재문의"</x:formula>
+      <x:formula>$K5="장기 대기 및 재문의"</x:formula>
     </x:cfRule>
     <x:cfRule type="expression" dxfId="2" priority="3">
       <x:formula>$K5="판매 준비 임박"</x:formula>
@@ -1409,7 +1409,7 @@
         <x:v>판단</x:v>
       </x:c>
       <x:c r="E4" s="19" t="str">
-        <x:v>협업·인계</x:v>
+        <x:v>협업 및 인계</x:v>
       </x:c>
       <x:c r="F4" s="19" t="str">
         <x:v>셀러 안내</x:v>
@@ -1464,7 +1464,7 @@
         <x:v>계약 지원과 완료 기준을 합의한 뒤 한 명이 통합 안내</x:v>
       </x:c>
       <x:c r="F6" s="12" t="str">
-        <x:v>수정할 항목·제출 위치·재확인 시간을 한 메시지로 전달</x:v>
+        <x:v>수정할 항목, 제출 위치, 재확인 시간</x:v>
       </x:c>
       <x:c r="G6" s="12" t="str">
         <x:v>보완 서류 접수와 정보 일치 확인</x:v>
@@ -1481,13 +1481,13 @@
         <x:v>실제 재고와 등록 재고가 다르고 주문 접수 알림 확인이 안 된 채 오픈이 하루 남음</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
-        <x:v>실재고·등록 수량, 품절 상품 노출, 주문 접수 기기·알림, 테스트 주문 결과</x:v>
+        <x:v>실재고와 등록 수량, 품절 상품 노출, 주문 접수 기기와 알림, 테스트 주문 결과</x:v>
       </x:c>
       <x:c r="D7" s="12" t="str">
         <x:v>오픈 일정만 맞추지 않고 주문 취소 가능성을 먼저 줄임</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>상품 운영과 주문 지원이 재고 수정·판매 중지 경로와 알림 상태를 함께 확인</x:v>
+        <x:v>상품 운영과 주문 지원이 재고 수정 또는 판매 중지 경로와 알림 상태를 함께 확인</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
         <x:v>수량 수정 또는 판매 중지 방법과 테스트 주문 확인 시간을 셀러에게 안내</x:v>
@@ -1521,7 +1521,7 @@
   <x:sheetData>
     <x:row r="1" ht="38" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>유관부서 협업·인계표</x:v>
+        <x:v>유관부서 협업 및 인계표</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1556,7 +1556,7 @@
     </x:row>
     <x:row r="5" ht="74" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>계약·영업</x:v>
+        <x:v>계약/영업</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
         <x:v>계약 상태, 필수 서류, 셀러와 합의한 일정</x:v>
@@ -1576,7 +1576,7 @@
         <x:v>정산</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>사업자·예금주·계좌 정보와 확인 이력</x:v>
+        <x:v>사업자, 예금주, 계좌 정보</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>불일치 원인과 수정 주체</x:v>
@@ -1593,7 +1593,7 @@
         <x:v>상품 운영</x:v>
       </x:c>
       <x:c r="B7" s="12" t="str">
-        <x:v>상품명·카테고리·이미지·옵션·상세 설명 상태</x:v>
+        <x:v>상품명, 카테고리, 이미지, 옵션, 상세 설명</x:v>
       </x:c>
       <x:c r="C7" s="12" t="str">
         <x:v>필수 수정과 오픈 이후 보완 가능 항목</x:v>
@@ -1607,7 +1607,7 @@
     </x:row>
     <x:row r="8" ht="74" customHeight="1">
       <x:c r="A8" s="12" t="str">
-        <x:v>CS·VOC</x:v>
+        <x:v>CS와 VOC</x:v>
       </x:c>
       <x:c r="B8" s="12" t="str">
         <x:v>문의 유형, 재문의 여부, 기존 답변과 해결 상태</x:v>
@@ -1627,7 +1627,7 @@
         <x:v>마케팅</x:v>
       </x:c>
       <x:c r="B9" s="12" t="str">
-        <x:v>프로모션 기간·가격·노출 문구와 재고 조건</x:v>
+        <x:v>프로모션 기간, 가격, 노출 문구</x:v>
       </x:c>
       <x:c r="C9" s="12" t="str">
         <x:v>셀러 설정과 캠페인 조건의 일치 여부</x:v>
@@ -1769,7 +1769,7 @@
         <x:v>사용을 멈출 때</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>재문의가 줄지 않거나 잘못된 연결이 늘면 문구 사용을 멈추고 화면·정책 원인을 다시 확인</x:v>
+        <x:v>화면이나 정책 원인</x:v>
       </x:c>
       <x:c r="C11" s="12"/>
       <x:c r="D11" s="12"/>
@@ -1788,7 +1788,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="12" t="str">
-        <x:v>배민스토어 상품 등록·수정 관리 · https://ceo.baemin.com/guide/11802</x:v>
+        <x:v>배민스토어 상품 등록 및 수정 관리 / https://ceo.baemin.com/guide/11802</x:v>
       </x:c>
       <x:c r="B14" s="12"/>
       <x:c r="C14" s="12"/>
@@ -1892,7 +1892,7 @@
         <x:v>7일 내 재문의율</x:v>
       </x:c>
       <x:c r="B6" s="12" t="str">
-        <x:v>같은 셀러·같은 문제의 7일 내 재문의 비율</x:v>
+        <x:v>같은 셀러의 같은 문제</x:v>
       </x:c>
       <x:c r="C6" s="12" t="str">
         <x:v>재문의 건 ÷ 문의 건</x:v>
@@ -1924,7 +1924,7 @@
         <x:v>긴 대기 꼬리 감소</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>완료·미완료 분리</x:v>
+        <x:v>완료/미완료 분리</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="60" customHeight="1">
@@ -2027,7 +2027,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="12" t="str">
-        <x:v>주문·재고</x:v>
+        <x:v>주문과 재고</x:v>
       </x:c>
       <x:c r="B15" s="12" t="str">
         <x:v>주문 취소와 재고 관리 노하우</x:v>
@@ -2044,7 +2044,7 @@
         <x:v>상품 등록</x:v>
       </x:c>
       <x:c r="B16" s="12" t="str">
-        <x:v>배민스토어 상품 등록·수정 관리</x:v>
+        <x:v>배민스토어 상품 등록 및 수정 관리</x:v>
       </x:c>
       <x:c r="C16" s="12" t="str">
         <x:v>https://ceo.baemin.com/guide/11802</x:v>
